--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,6 +1588,257 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129193697</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stiftets granskog II, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>376316</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557378</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Tveta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fick vänta länge på att få se den svartvita ryggen, så jag kunde vara helt säker.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129193771</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stiftets granskog II, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>376316</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6557378</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Tveta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>129193697</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129193771</v>
       </c>
       <c r="B10" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>129193697</v>
       </c>
       <c r="B9" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129193771</v>
       </c>
       <c r="B10" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -1593,7 +1593,7 @@
         <v>129193697</v>
       </c>
       <c r="B9" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>129193771</v>
       </c>
       <c r="B10" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -675,50 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56755194</v>
+        <v>111757893</v>
       </c>
       <c r="B2" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>3277</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mossvik, väg S532, Vrm</t>
+          <t>Mossvik granplantering, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>376268.7737220219</v>
+        <v>376336</v>
       </c>
       <c r="R2" t="n">
-        <v>6557328.859269861</v>
+        <v>6557398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-02</t>
+          <t>2023-08-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Många fler än på bild, men räknade dom inte.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,59 +780,46 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>John Rolander Borlid</t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mats Lindqvist, Gabriella Malmborg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79622847</v>
+        <v>129193697</v>
       </c>
       <c r="B3" t="n">
-        <v>57140</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100088</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,18 +832,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -853,14 +846,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mossvik granplantering, Vrm</t>
+          <t>Stiftets granskog II, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>376336.3292309065</v>
+        <v>376316</v>
       </c>
       <c r="R3" t="n">
-        <v>6557397.533110926</v>
+        <v>6557378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,22 +880,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-26</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fick vänta länge på att få se den svartvita ryggen, så jag kunde vara helt säker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,34 +909,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingrid Törnqvist </t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingrid Törnqvist </t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101866957</v>
+        <v>79622847</v>
       </c>
       <c r="B4" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56895</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -946,16 +938,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208260</v>
+        <v>100088</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -979,11 +971,7 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -995,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>376336.3292309065</v>
+        <v>376336</v>
       </c>
       <c r="R4" t="n">
-        <v>6557397.533110926</v>
+        <v>6557398</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,27 +1013,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Låg på asfalt. Föste ner den i diket. har sett för många trafikdödade ormar.</t>
+          <t>2019-08-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1061,73 +1034,73 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingrid Törnqvist </t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingrid Törnqvist </t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111757893</v>
+        <v>129193771</v>
       </c>
       <c r="B5" t="n">
-        <v>89462</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3277</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mossvik granplantering, Vrm</t>
+          <t>Stiftets granskog II, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>376336</v>
+        <v>376316</v>
       </c>
       <c r="R5" t="n">
-        <v>6557398</v>
+        <v>6557378</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1154,27 +1127,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Många fler än på bild, men räknade dom inte.</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,84 +1151,91 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingrid Törnqvist </t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingrid Törnqvist </t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117993478</v>
+        <v>123726473</v>
       </c>
       <c r="B6" t="n">
-        <v>108714</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sjöbråten, Vrm</t>
+          <t>väg 532, N Grorudsvägen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>376252</v>
+        <v>376303</v>
       </c>
       <c r="R6" t="n">
-        <v>6557268</v>
+        <v>6557350</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1284,27 +1259,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Västra sidan hela vägområdet</t>
+          <t>Har sett 4 trafikdödade på några dagar på en vägsträcka  ca 2km. Brukar vara så varje år, då grodor o paddor ska korsa vägen inför parningssäsongen. Ändå inte så mycket trafik.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1313,37 +1288,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>victoria höglund</t>
+          <t>Ingrid Törnqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>victoria höglund</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
-        </is>
-      </c>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122985391</v>
+        <v>101866957</v>
       </c>
       <c r="B7" t="n">
-        <v>96960</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,41 +1318,62 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>208260</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stiftets granskog, Vrm</t>
+          <t>Mossvik granplantering, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>376299</v>
+        <v>376336</v>
       </c>
       <c r="R7" t="n">
-        <v>6557402</v>
+        <v>6557398</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,17 +1397,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2022-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2022-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ca 10 m2</t>
+          <t>Låg på asfalt. Föste ner den i diket. har sett för många trafikdödade ormar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1447,15 +1445,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123726473</v>
+        <v>56755194</v>
       </c>
       <c r="B8" t="n">
-        <v>58373</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,62 +1456,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208249</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>väg 532, N Grorudsvägen, Vrm</t>
+          <t>Mossvik, väg S532, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>376303</v>
+        <v>376269</v>
       </c>
       <c r="R8" t="n">
-        <v>6557350</v>
+        <v>6557329</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,27 +1510,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2013-07-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Har sett 4 trafikdödade på några dagar på en vägsträcka  ca 2km. Brukar vara så varje år, då grodor o paddor ska korsa vägen inför parningssäsongen. Ändå inte så mycket trafik.</t>
+          <t>2013-07-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,29 +1524,37 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ingrid Törnqvist</t>
+          <t>John Rolander Borlid</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingrid Törnqvist</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Mats Lindqvist, Gabriella Malmborg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129193697</v>
+        <v>117993478</v>
       </c>
       <c r="B9" t="n">
-        <v>57743</v>
+        <v>110078</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,53 +1562,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>220299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stiftets granskog II, Vrm</t>
+          <t>Sjöbråten, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>376316</v>
+        <v>376252</v>
       </c>
       <c r="R9" t="n">
-        <v>6557378</v>
+        <v>6557268</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1671,27 +1628,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fick vänta länge på att få se den svartvita ryggen, så jag kunde vara helt säker.</t>
+          <t>Västra sidan hela vägområdet</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1706,22 +1663,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ingrid Törnqvist</t>
+          <t>victoria höglund</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ingrid Törnqvist</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>victoria höglund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129193771</v>
+        <v>122985391</v>
       </c>
       <c r="B10" t="n">
-        <v>58100</v>
+        <v>97986</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1729,53 +1690,41 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>221946</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stiftets granskog II, Vrm</t>
+          <t>Stiftets granskog, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>376316</v>
+        <v>376299</v>
       </c>
       <c r="R10" t="n">
-        <v>6557378</v>
+        <v>6557402</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1799,22 +1748,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>12:40</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>12:55</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 10 m2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1823,6 +1767,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,6 +1784,125 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134640418</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99115</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mossvik granplantering, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>376336</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6557398</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säffle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Tveta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Räknade till 230 där de växte glesare. Platsen där de flesta fanns uppskattades till ca 500. I andra delar av vägens diken mellan Sjöbykorset och Mossvik växer det många dessutom. Väg 532 Säffle.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ingrid Törnqvist</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44253-2025 artfynd.xlsx
+++ b/artfynd/A 44253-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111757893</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193697</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79622847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129193771</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1304,6 +1329,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123726473</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1442,6 +1472,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101866957</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1548,6 +1583,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56755194</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1674,6 +1714,11 @@
       <c r="AY9" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117993478</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1828,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122985391</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1902,8 +1952,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134640418</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>